--- a/Hand_edited_log/1/student/cuongnvhe181200/TC4/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/cuongnvhe181200/TC4/GradeDetail.xlsx
@@ -188,6 +188,9 @@
     <x:t>S001</x:t>
   </x:si>
   <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
@@ -201,9 +204,6 @@
   </x:si>
   <x:si>
     <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
@@ -247,12 +247,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1062,10 +1062,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1118,10 +1118,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,10 +1174,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1230,10 +1230,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
         <x:v>46</x:v>
@@ -1277,22 +1277,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4000</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>55762</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1327,7 +1327,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1347,8 +1347,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>57</x:v>
+      <x:c r="R7" s="4" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1389,22 +1389,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>55762</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>51729</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1424,25 +1424,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>45</x:v>
@@ -1454,13 +1454,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55762</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>51729</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1510,10 +1510,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1536,22 +1536,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>62</x:v>
@@ -1566,13 +1566,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55762</x:v>
+        <x:v>51729</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1607,7 +1607,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1627,8 +1627,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>57</x:v>
+      <x:c r="R12" s="4" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
